--- a/artfynd/A 61763-2025 artfynd.xlsx
+++ b/artfynd/A 61763-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>130146915</v>
       </c>
       <c r="B5" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61763-2025 artfynd.xlsx
+++ b/artfynd/A 61763-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130154664</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130154657</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130146915</v>
       </c>
       <c r="B5" t="n">
-        <v>92294</v>
+        <v>92381</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61763-2025 artfynd.xlsx
+++ b/artfynd/A 61763-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130146915</v>
       </c>
       <c r="B5" t="n">
-        <v>92381</v>
+        <v>92384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61763-2025 artfynd.xlsx
+++ b/artfynd/A 61763-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130154664</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130154657</v>
       </c>
       <c r="B3" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130146915</v>
       </c>
       <c r="B5" t="n">
-        <v>92384</v>
+        <v>92410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61763-2025 artfynd.xlsx
+++ b/artfynd/A 61763-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130146915</v>
       </c>
       <c r="B5" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61763-2025 artfynd.xlsx
+++ b/artfynd/A 61763-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130146915</v>
       </c>
       <c r="B5" t="n">
-        <v>92411</v>
+        <v>92412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61763-2025 artfynd.xlsx
+++ b/artfynd/A 61763-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130154664</v>
+        <v>130154662</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688264</v>
+        <v>688237</v>
       </c>
       <c r="R2" t="n">
-        <v>6614892</v>
+        <v>6614926</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130154657</v>
+        <v>130154666</v>
       </c>
       <c r="B3" t="n">
-        <v>58224</v>
+        <v>97776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>1590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harsjön, Upl</t>
+          <t>300m Ö Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688236</v>
+        <v>688464</v>
       </c>
       <c r="R3" t="n">
-        <v>6615105</v>
+        <v>6614959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130154654</v>
+        <v>130154665</v>
       </c>
       <c r="B4" t="n">
-        <v>8440</v>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Harsjön, Upl</t>
+          <t>300m Ö Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688222</v>
+        <v>688466</v>
       </c>
       <c r="R4" t="n">
-        <v>6615113</v>
+        <v>6614956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130146915</v>
+        <v>130154661</v>
       </c>
       <c r="B5" t="n">
-        <v>92412</v>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harsjön, Harsjön, Upl</t>
+          <t>Harsjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>688214</v>
+        <v>688229</v>
       </c>
       <c r="R5" t="n">
-        <v>6615083</v>
+        <v>6614944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,15 +1091,560 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130146915</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Harsjön, Harsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>688214</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6615083</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130154657</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Harsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>688236</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6615105</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130154664</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Harsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>688264</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6614892</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130154659</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Harsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>688205</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6615101</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130154654</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Harsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>688222</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6615113</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
